--- a/public/templates/base-clientes-modelo.xlsx
+++ b/public/templates/base-clientes-modelo.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -479,7 +479,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>11222333000144</v>
+        <v>11222333000181</v>
       </c>
       <c r="B4" t="str">
         <v>IMPORTADORA GAMMA LTDA</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>99888777000166</v>
+        <v>99888777000100</v>
       </c>
       <c r="B5" t="str">
         <v>LOGISTICA DELTA COMERCIO EXTERIOR LTDA</v>
